--- a/700 HK.xlsx
+++ b/700 HK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFF8C68-A775-4D45-8080-DCA99B34D999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3AA638-0F8B-4AB4-96B0-D272DBC453A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18910" yWindow="6660" windowWidth="19170" windowHeight="13220" xr2:uid="{C183CDF4-DAE3-4211-A459-AE4D0C2142B8}"/>
+    <workbookView xWindow="18040" yWindow="7930" windowWidth="19890" windowHeight="10280" activeTab="1" xr2:uid="{C183CDF4-DAE3-4211-A459-AE4D0C2142B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="104">
   <si>
     <t>Price HKD</t>
   </si>
@@ -333,6 +333,21 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Billion RMB</t>
   </si>
 </sst>
 </file>
@@ -442,13 +457,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
@@ -1022,21 +1037,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{666C0D08-E52C-4128-A040-0E26B040CE26}">
-  <dimension ref="A1:AR53"/>
+  <dimension ref="A1:AV53"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.81640625" customWidth="1"/>
     <col min="3" max="14" width="9.1796875" style="2"/>
-    <col min="15" max="26" width="8.7265625" style="2"/>
+    <col min="15" max="30" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
@@ -1109,71 +1127,83 @@
       <c r="Z2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="AC2">
+      <c r="AA2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG2">
         <v>2020</v>
       </c>
-      <c r="AD2">
-        <f>AC2+1</f>
+      <c r="AH2">
+        <f>AG2+1</f>
         <v>2021</v>
       </c>
-      <c r="AE2">
-        <f t="shared" ref="AE2:AR2" si="0">AD2+1</f>
+      <c r="AI2">
+        <f t="shared" ref="AI2:AV2" si="0">AH2+1</f>
         <v>2022</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <f t="shared" si="0"/>
         <v>2033</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <f t="shared" si="0"/>
         <v>2034</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <f t="shared" si="0"/>
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>72</v>
       </c>
@@ -1215,8 +1245,12 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
-    </row>
-    <row r="4" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
+    </row>
+    <row r="4" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>73</v>
       </c>
@@ -1258,8 +1292,12 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
-    </row>
-    <row r="5" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4"/>
+      <c r="AD4" s="4"/>
+    </row>
+    <row r="5" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>75</v>
       </c>
@@ -1301,8 +1339,54 @@
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
-    </row>
-    <row r="7" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="4"/>
+    </row>
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="S6" s="4">
+        <f t="shared" ref="S6:U6" si="1">S7-S11-S12-S13</f>
+        <v>29</v>
+      </c>
+      <c r="T6" s="4">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="U6" s="4">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+      <c r="V6" s="4">
+        <f t="shared" ref="V6" si="2">V7-V11-V12-V13</f>
+        <v>22</v>
+      </c>
+      <c r="W6" s="4">
+        <f t="shared" ref="W6:X6" si="3">W7-W11-W12-W13</f>
+        <v>33</v>
+      </c>
+      <c r="X6" s="4">
+        <f t="shared" si="3"/>
+        <v>-32</v>
+      </c>
+      <c r="Y6" s="4">
+        <f t="shared" ref="Y6:Z6" si="4">Y7-Y11-Y12-Y13</f>
+        <v>-40</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="AA6" s="4">
+        <f>AA7-AA11-AA12-AA13</f>
+        <v>10</v>
+      </c>
+      <c r="AB6" s="4">
+        <f>AB7-AB11-AB12-AB13</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1348,27 +1432,51 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
-      <c r="AC7" s="3">
+      <c r="S7" s="4">
+        <v>78629</v>
+      </c>
+      <c r="T7" s="4">
+        <v>78822</v>
+      </c>
+      <c r="U7" s="4">
+        <v>82695</v>
+      </c>
+      <c r="V7" s="4">
+        <v>79022</v>
+      </c>
+      <c r="W7" s="4">
+        <v>92133</v>
+      </c>
+      <c r="X7" s="4">
+        <v>91368</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>95860</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>89920</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>96110</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>98414</v>
+      </c>
+      <c r="AC7" s="4"/>
+      <c r="AD7" s="4"/>
+      <c r="AG7" s="3">
         <v>264212</v>
       </c>
-      <c r="AD7" s="3">
+      <c r="AH7" s="3">
         <f>SUM(G7:J7)</f>
         <v>291572</v>
       </c>
-      <c r="AE7" s="3">
+      <c r="AI7" s="3">
         <f>SUM(K7:N7)</f>
         <v>292942.36</v>
       </c>
     </row>
-    <row r="8" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
@@ -1400,8 +1508,12 @@
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
-    </row>
-    <row r="9" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+    </row>
+    <row r="9" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>54</v>
       </c>
@@ -1433,8 +1545,12 @@
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
-    </row>
-    <row r="10" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+    </row>
+    <row r="10" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>65</v>
       </c>
@@ -1468,8 +1584,12 @@
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
-    </row>
-    <row r="11" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="4"/>
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4"/>
+    </row>
+    <row r="11" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>55</v>
       </c>
@@ -1493,16 +1613,40 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-    </row>
-    <row r="12" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S11" s="4">
+        <v>34500</v>
+      </c>
+      <c r="T11" s="4">
+        <v>34600</v>
+      </c>
+      <c r="U11" s="4">
+        <v>37300</v>
+      </c>
+      <c r="V11" s="4">
+        <v>29800</v>
+      </c>
+      <c r="W11" s="4">
+        <v>42900</v>
+      </c>
+      <c r="X11" s="4">
+        <v>40400</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>42800</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>38200</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>45400</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>47300</v>
+      </c>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4"/>
+    </row>
+    <row r="12" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>56</v>
       </c>
@@ -1526,16 +1670,40 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-    </row>
-    <row r="13" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S12" s="4">
+        <v>13600</v>
+      </c>
+      <c r="T12" s="4">
+        <v>13900</v>
+      </c>
+      <c r="U12" s="4">
+        <v>14500</v>
+      </c>
+      <c r="V12" s="4">
+        <v>16000</v>
+      </c>
+      <c r="W12" s="4">
+        <v>16600</v>
+      </c>
+      <c r="X12" s="4">
+        <v>18800</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>20800</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>21100</v>
+      </c>
+      <c r="AA12" s="4">
+        <v>18800</v>
+      </c>
+      <c r="AB12" s="4">
+        <v>18600</v>
+      </c>
+      <c r="AC12" s="4"/>
+      <c r="AD12" s="4"/>
+    </row>
+    <row r="13" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>66</v>
       </c>
@@ -1559,16 +1727,40 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-    </row>
-    <row r="14" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S13" s="4">
+        <v>30500</v>
+      </c>
+      <c r="T13" s="4">
+        <v>30300</v>
+      </c>
+      <c r="U13" s="4">
+        <v>30900</v>
+      </c>
+      <c r="V13" s="4">
+        <v>33200</v>
+      </c>
+      <c r="W13" s="4">
+        <v>32600</v>
+      </c>
+      <c r="X13" s="4">
+        <v>32200</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>32300</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>30600</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>31900</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>32500</v>
+      </c>
+      <c r="AC13" s="4"/>
+      <c r="AD13" s="4"/>
+    </row>
+    <row r="14" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -1593,8 +1785,12 @@
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
-    </row>
-    <row r="15" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA14" s="4"/>
+      <c r="AB14" s="4"/>
+      <c r="AC14" s="4"/>
+      <c r="AD14" s="4"/>
+    </row>
+    <row r="15" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>19</v>
       </c>
@@ -1640,27 +1836,51 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4"/>
-      <c r="AC15" s="3">
+      <c r="S15" s="4">
+        <v>26506</v>
+      </c>
+      <c r="T15" s="4">
+        <v>29871</v>
+      </c>
+      <c r="U15" s="4">
+        <v>29993</v>
+      </c>
+      <c r="V15" s="4">
+        <v>35004</v>
+      </c>
+      <c r="W15" s="4">
+        <v>31853</v>
+      </c>
+      <c r="X15" s="4">
+        <v>35762</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>36242</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>41116</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>38171</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>43565</v>
+      </c>
+      <c r="AC15" s="4"/>
+      <c r="AD15" s="4"/>
+      <c r="AG15" s="3">
         <v>82271</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AH15" s="3">
         <f>SUM(G15:J15)</f>
         <v>88666</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AI15" s="3">
         <f>SUM(K15:N15)</f>
         <v>80198.87</v>
       </c>
     </row>
-    <row r="16" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:48" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>20</v>
       </c>
@@ -1706,27 +1926,51 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
-      <c r="AC16" s="3">
+      <c r="S16" s="4">
+        <v>52302</v>
+      </c>
+      <c r="T16" s="4">
+        <v>50440</v>
+      </c>
+      <c r="U16" s="4">
+        <v>53089</v>
+      </c>
+      <c r="V16" s="4">
+        <v>56125</v>
+      </c>
+      <c r="W16" s="4">
+        <v>54907</v>
+      </c>
+      <c r="X16" s="4">
+        <v>55536</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>58174</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>60818</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>59885</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>60289</v>
+      </c>
+      <c r="AC16" s="4"/>
+      <c r="AD16" s="4"/>
+      <c r="AG16" s="3">
         <v>128086</v>
       </c>
-      <c r="AD16" s="3">
+      <c r="AH16" s="3">
         <f>SUM(G16:J16)</f>
         <v>172195</v>
       </c>
-      <c r="AE16" s="3">
+      <c r="AI16" s="3">
         <f>SUM(K16:N16)</f>
         <v>177163.75</v>
       </c>
     </row>
-    <row r="17" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
@@ -1772,60 +2016,84 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
-      <c r="AC17" s="3">
+      <c r="S17" s="4">
+        <v>2064</v>
+      </c>
+      <c r="T17" s="4">
+        <v>1984</v>
+      </c>
+      <c r="U17" s="4">
+        <v>1416</v>
+      </c>
+      <c r="V17" s="4">
+        <v>2295</v>
+      </c>
+      <c r="W17" s="4">
+        <v>1129</v>
+      </c>
+      <c r="X17" s="4">
+        <v>1838</v>
+      </c>
+      <c r="Y17" s="4">
+        <v>2593</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>2517</v>
+      </c>
+      <c r="AA17" s="4">
+        <v>2292</v>
+      </c>
+      <c r="AB17" s="4">
+        <v>2520</v>
+      </c>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AG17" s="3">
         <v>7495</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AH17" s="3">
         <f>SUM(G17:J17)</f>
         <v>7685</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AI17" s="3">
         <f>SUM(K17:N17)</f>
         <v>7675.52</v>
       </c>
     </row>
-    <row r="18" spans="2:36" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:40" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="6">
-        <f t="shared" ref="C18" si="1">C17+C16+C15+C7</f>
+        <f t="shared" ref="C18" si="5">C17+C16+C15+C7</f>
         <v>108065</v>
       </c>
       <c r="D18" s="6">
-        <f t="shared" ref="D18" si="2">D17+D16+D15+D7</f>
+        <f t="shared" ref="D18" si="6">D17+D16+D15+D7</f>
         <v>114883</v>
       </c>
       <c r="E18" s="6">
-        <f t="shared" ref="E18:J18" si="3">E17+E16+E15+E7</f>
+        <f t="shared" ref="E18:J18" si="7">E17+E16+E15+E7</f>
         <v>125447</v>
       </c>
       <c r="F18" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>133669</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>135303</v>
       </c>
       <c r="H18" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>138259</v>
       </c>
       <c r="I18" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>142368</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>144188</v>
       </c>
       <c r="K18" s="6">
@@ -1844,52 +2112,104 @@
         <f>N17+N16+N15+N7</f>
         <v>146637.78</v>
       </c>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
+      <c r="O18" s="6">
+        <f t="shared" ref="O18:AD18" si="8">O17+O16+O15+O7</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="6">
+        <f t="shared" si="8"/>
+        <v>159501</v>
+      </c>
+      <c r="T18" s="6">
+        <f t="shared" si="8"/>
+        <v>161117</v>
+      </c>
+      <c r="U18" s="6">
+        <f t="shared" si="8"/>
+        <v>167193</v>
+      </c>
+      <c r="V18" s="6">
+        <f t="shared" si="8"/>
+        <v>172446</v>
+      </c>
+      <c r="W18" s="6">
+        <f t="shared" si="8"/>
+        <v>180022</v>
+      </c>
+      <c r="X18" s="6">
+        <f t="shared" si="8"/>
+        <v>184504</v>
+      </c>
+      <c r="Y18" s="6">
+        <f t="shared" si="8"/>
+        <v>192869</v>
+      </c>
+      <c r="Z18" s="6">
+        <f t="shared" si="8"/>
+        <v>194371</v>
+      </c>
+      <c r="AA18" s="6">
+        <f t="shared" si="8"/>
+        <v>196458</v>
+      </c>
+      <c r="AB18" s="6">
+        <f t="shared" si="8"/>
+        <v>204788</v>
+      </c>
       <c r="AC18" s="6">
-        <f t="shared" ref="AC18:AJ18" si="4">AC17+AC16+AC15+AC7</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG18" s="6">
+        <f t="shared" ref="AG18:AN18" si="9">AG17+AG16+AG15+AG7</f>
         <v>482064</v>
       </c>
-      <c r="AD18" s="6">
-        <f t="shared" si="4"/>
+      <c r="AH18" s="6">
+        <f t="shared" si="9"/>
         <v>560118</v>
       </c>
-      <c r="AE18" s="6">
-        <f t="shared" si="4"/>
+      <c r="AI18" s="6">
+        <f t="shared" si="9"/>
         <v>557980.5</v>
       </c>
-      <c r="AF18" s="6">
-        <f t="shared" si="4"/>
+      <c r="AJ18" s="6">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AG18" s="6">
-        <f t="shared" si="4"/>
+      <c r="AK18" s="6">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AH18" s="6">
-        <f t="shared" si="4"/>
+      <c r="AL18" s="6">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AI18" s="6">
-        <f t="shared" si="4"/>
+      <c r="AM18" s="6">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ18" s="6">
-        <f t="shared" si="4"/>
+      <c r="AN18" s="6">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
@@ -1935,59 +2255,83 @@
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-      <c r="AC19" s="3">
+      <c r="S19" s="4">
+        <v>75631</v>
+      </c>
+      <c r="T19" s="4">
+        <v>75222</v>
+      </c>
+      <c r="U19" s="4">
+        <v>78365</v>
+      </c>
+      <c r="V19" s="4">
+        <v>81793</v>
+      </c>
+      <c r="W19" s="4">
+        <v>79529</v>
+      </c>
+      <c r="X19" s="4">
+        <v>79491</v>
+      </c>
+      <c r="Y19" s="4">
+        <v>84071</v>
+      </c>
+      <c r="Z19" s="4">
+        <v>86082</v>
+      </c>
+      <c r="AA19" s="4">
+        <v>85193</v>
+      </c>
+      <c r="AB19" s="4">
+        <v>86352</v>
+      </c>
+      <c r="AC19" s="4"/>
+      <c r="AD19" s="4"/>
+      <c r="AG19" s="3">
         <v>260532</v>
       </c>
-      <c r="AD19" s="3">
+      <c r="AH19" s="3">
         <v>314174</v>
       </c>
-      <c r="AE19" s="3">
+      <c r="AI19" s="3">
         <f>SUM(K19:N19)</f>
         <v>316110.28000000003</v>
       </c>
     </row>
-    <row r="20" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="4">
-        <f t="shared" ref="C20" si="5">C18-C19</f>
+        <f t="shared" ref="C20" si="10">C18-C19</f>
         <v>52794</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" ref="D20" si="6">D18-D19</f>
+        <f t="shared" ref="D20" si="11">D18-D19</f>
         <v>53210</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" ref="E20:F20" si="7">E18-E19</f>
+        <f t="shared" ref="E20:F20" si="12">E18-E19</f>
         <v>56647</v>
       </c>
       <c r="F20" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>58881</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" ref="G20:J20" si="8">G18-G19</f>
+        <f t="shared" ref="G20:J20" si="13">G18-G19</f>
         <v>62635</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>62745</v>
       </c>
       <c r="I20" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>62747</v>
       </c>
       <c r="J20" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>57817</v>
       </c>
       <c r="K20" s="4">
@@ -2010,28 +2354,62 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="4"/>
-      <c r="AC20" s="3">
-        <f t="shared" ref="AC20" si="9">AC18-AC19</f>
+      <c r="S20" s="4">
+        <f>+S18-S19</f>
+        <v>83870</v>
+      </c>
+      <c r="T20" s="4">
+        <f>+T18-T19</f>
+        <v>85895</v>
+      </c>
+      <c r="U20" s="4">
+        <f>+U18-U19</f>
+        <v>88828</v>
+      </c>
+      <c r="V20" s="4">
+        <f>+V18-V19</f>
+        <v>90653</v>
+      </c>
+      <c r="W20" s="4">
+        <f>+W18-W19</f>
+        <v>100493</v>
+      </c>
+      <c r="X20" s="4">
+        <f>+X18-X19</f>
+        <v>105013</v>
+      </c>
+      <c r="Y20" s="4">
+        <f>+Y18-Y19</f>
+        <v>108798</v>
+      </c>
+      <c r="Z20" s="4">
+        <f>+Z18-Z19</f>
+        <v>108289</v>
+      </c>
+      <c r="AA20" s="4">
+        <f>+AA18-AA19</f>
+        <v>111265</v>
+      </c>
+      <c r="AB20" s="4">
+        <f>+AB18-AB19</f>
+        <v>118436</v>
+      </c>
+      <c r="AC20" s="4"/>
+      <c r="AD20" s="4"/>
+      <c r="AG20" s="3">
+        <f t="shared" ref="AG20" si="14">AG18-AG19</f>
         <v>221532</v>
       </c>
-      <c r="AD20" s="3">
-        <f>AD18-AD19</f>
+      <c r="AH20" s="3">
+        <f>AH18-AH19</f>
         <v>245944</v>
       </c>
-      <c r="AE20" s="3">
-        <f>AE18-AE19</f>
+      <c r="AI20" s="3">
+        <f>AI18-AI19</f>
         <v>241870.21999999997</v>
       </c>
     </row>
-    <row r="21" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
@@ -2085,18 +2463,22 @@
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
-      <c r="AC21" s="3">
+      <c r="AA21" s="4"/>
+      <c r="AB21" s="4"/>
+      <c r="AC21" s="4"/>
+      <c r="AD21" s="4"/>
+      <c r="AG21" s="3">
         <v>67625</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AH21" s="3">
         <v>89847</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AI21" s="3">
         <f>SUM(K21:N21)</f>
         <v>98731.9</v>
       </c>
     </row>
-    <row r="22" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>25</v>
       </c>
@@ -2150,51 +2532,55 @@
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
-      <c r="AC22" s="3">
+      <c r="AA22" s="4"/>
+      <c r="AB22" s="4"/>
+      <c r="AC22" s="4"/>
+      <c r="AD22" s="4"/>
+      <c r="AG22" s="3">
         <v>33758</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AH22" s="3">
         <v>40594</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AI22" s="3">
         <f>SUM(K22:N22)</f>
         <v>36938.449999999997</v>
       </c>
     </row>
-    <row r="23" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C23" s="4">
-        <f t="shared" ref="C23" si="10">C21+C22</f>
+        <f t="shared" ref="C23" si="15">C21+C22</f>
         <v>21207</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" ref="D23" si="11">D21+D22</f>
+        <f t="shared" ref="D23" si="16">D21+D22</f>
         <v>24255</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" ref="E23" si="12">E21+E22</f>
+        <f t="shared" ref="E23" si="17">E21+E22</f>
         <v>26109</v>
       </c>
       <c r="F23" s="4">
-        <f t="shared" ref="F23" si="13">F21+F22</f>
+        <f t="shared" ref="F23" si="18">F21+F22</f>
         <v>29812</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" ref="G23:J23" si="14">G21+G22</f>
+        <f t="shared" ref="G23:J23" si="19">G21+G22</f>
         <v>27497</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>32651</v>
       </c>
       <c r="I23" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>34297</v>
       </c>
       <c r="J23" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>35996</v>
       </c>
       <c r="K23" s="4">
@@ -2206,11 +2592,11 @@
         <v>34165</v>
       </c>
       <c r="M23" s="4">
-        <f t="shared" ref="M23:N23" si="15">M21+M22</f>
+        <f t="shared" ref="M23:N23" si="20">M21+M22</f>
         <v>32582.149999999998</v>
       </c>
       <c r="N23" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>34196.199999999997</v>
       </c>
       <c r="O23" s="4"/>
@@ -2225,53 +2611,57 @@
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
-      <c r="AC23" s="3">
-        <f t="shared" ref="AC23" si="16">AC21+AC22</f>
+      <c r="AA23" s="4"/>
+      <c r="AB23" s="4"/>
+      <c r="AC23" s="4"/>
+      <c r="AD23" s="4"/>
+      <c r="AG23" s="3">
+        <f t="shared" ref="AG23" si="21">AG21+AG22</f>
         <v>101383</v>
       </c>
-      <c r="AD23" s="3">
-        <f>AD21+AD22</f>
+      <c r="AH23" s="3">
+        <f>AH21+AH22</f>
         <v>130441</v>
       </c>
-      <c r="AE23" s="3">
-        <f>AE21+AE22</f>
+      <c r="AI23" s="3">
+        <f>AI21+AI22</f>
         <v>135670.34999999998</v>
       </c>
     </row>
-    <row r="24" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C24" s="4">
-        <f t="shared" ref="C24" si="17">C20-C23</f>
+        <f t="shared" ref="C24" si="22">C20-C23</f>
         <v>31587</v>
       </c>
       <c r="D24" s="4">
-        <f t="shared" ref="D24" si="18">D20-D23</f>
+        <f t="shared" ref="D24" si="23">D20-D23</f>
         <v>28955</v>
       </c>
       <c r="E24" s="4">
-        <f t="shared" ref="E24" si="19">E20-E23</f>
+        <f t="shared" ref="E24" si="24">E20-E23</f>
         <v>30538</v>
       </c>
       <c r="F24" s="4">
-        <f t="shared" ref="F24" si="20">F20-F23</f>
+        <f t="shared" ref="F24" si="25">F20-F23</f>
         <v>29069</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" ref="G24:J24" si="21">G20-G23</f>
+        <f t="shared" ref="G24:J24" si="26">G20-G23</f>
         <v>35138</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>30094</v>
       </c>
       <c r="I24" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>28450</v>
       </c>
       <c r="J24" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>21821</v>
       </c>
       <c r="K24" s="4">
@@ -2283,11 +2673,11 @@
         <v>23702</v>
       </c>
       <c r="M24" s="4">
-        <f t="shared" ref="M24:N24" si="22">M20-M23</f>
+        <f t="shared" ref="M24:N24" si="27">M20-M23</f>
         <v>29826.446800000002</v>
       </c>
       <c r="N24" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>30324.423200000005</v>
       </c>
       <c r="O24" s="4"/>
@@ -2302,20 +2692,24 @@
       <c r="X24" s="4"/>
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
-      <c r="AC24" s="3">
-        <f t="shared" ref="AC24" si="23">AC20-AC23</f>
+      <c r="AA24" s="4"/>
+      <c r="AB24" s="4"/>
+      <c r="AC24" s="4"/>
+      <c r="AD24" s="4"/>
+      <c r="AG24" s="3">
+        <f t="shared" ref="AG24" si="28">AG20-AG23</f>
         <v>120149</v>
       </c>
-      <c r="AD24" s="3">
-        <f>AD20-AD23</f>
+      <c r="AH24" s="3">
+        <f>AH20-AH23</f>
         <v>115503</v>
       </c>
-      <c r="AE24" s="3">
-        <f>AE20-AE23</f>
+      <c r="AI24" s="3">
+        <f>AI20-AI23</f>
         <v>106199.87</v>
       </c>
     </row>
-    <row r="25" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>31</v>
       </c>
@@ -2379,53 +2773,57 @@
       <c r="X25" s="4"/>
       <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
-      <c r="AC25" s="3">
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AG25" s="3">
         <f>6957+57131-7887+3672</f>
         <v>59873</v>
       </c>
-      <c r="AD25" s="3">
+      <c r="AH25" s="3">
         <f>6650+149467-7114-16444</f>
         <v>132559</v>
       </c>
-      <c r="AE25" s="3">
+      <c r="AI25" s="3">
         <f>SUM(K25:N25)</f>
         <v>59631.75</v>
       </c>
     </row>
-    <row r="26" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="4">
-        <f t="shared" ref="C26" si="24">C24+C25</f>
+        <f t="shared" ref="C26" si="29">C24+C25</f>
         <v>35295</v>
       </c>
       <c r="D26" s="4">
-        <f t="shared" ref="D26" si="25">D24+D25</f>
+        <f t="shared" ref="D26" si="30">D24+D25</f>
         <v>37011</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" ref="E26:F26" si="26">E24+E25</f>
+        <f t="shared" ref="E26:F26" si="31">E24+E25</f>
         <v>44638</v>
       </c>
       <c r="F26" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>63078</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" ref="G26:J26" si="27">G24+G25</f>
+        <f t="shared" ref="G26:J26" si="32">G24+G25</f>
         <v>56254</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>46688</v>
       </c>
       <c r="I26" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>45527</v>
       </c>
       <c r="J26" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>99593</v>
       </c>
       <c r="K26" s="4">
@@ -2437,11 +2835,11 @@
         <v>23798</v>
       </c>
       <c r="M26" s="4">
-        <f t="shared" ref="M26:N26" si="28">M24+M25</f>
+        <f t="shared" ref="M26:N26" si="33">M24+M25</f>
         <v>55226.446800000005</v>
       </c>
       <c r="N26" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>57805.173200000005</v>
       </c>
       <c r="O26" s="4"/>
@@ -2456,20 +2854,24 @@
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
-      <c r="AC26" s="3">
-        <f>AC24+AC25</f>
+      <c r="AA26" s="4"/>
+      <c r="AB26" s="4"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AG26" s="3">
+        <f>AG24+AG25</f>
         <v>180022</v>
       </c>
-      <c r="AD26" s="3">
-        <f>AD24+AD25</f>
+      <c r="AH26" s="3">
+        <f>AH24+AH25</f>
         <v>248062</v>
       </c>
-      <c r="AE26" s="3">
-        <f>AE24+AE25</f>
+      <c r="AI26" s="3">
+        <f>AI24+AI25</f>
         <v>165831.62</v>
       </c>
     </row>
-    <row r="27" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>29</v>
       </c>
@@ -2532,53 +2934,57 @@
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
       <c r="Z27" s="4"/>
-      <c r="AC27" s="3">
+      <c r="AA27" s="4"/>
+      <c r="AB27" s="4"/>
+      <c r="AC27" s="4"/>
+      <c r="AD27" s="4"/>
+      <c r="AG27" s="3">
         <f>19897+278</f>
         <v>20175</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AH27" s="3">
         <f>20252+2988</f>
         <v>23240</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AI27" s="3">
         <f>SUM(K27:N27)</f>
         <v>27111.743000000002</v>
       </c>
     </row>
-    <row r="28" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C28" s="4">
-        <f t="shared" ref="C28" si="29">C26-C27</f>
+        <f t="shared" ref="C28" si="34">C26-C27</f>
         <v>28896</v>
       </c>
       <c r="D28" s="4">
-        <f t="shared" ref="D28" si="30">D26-D27</f>
+        <f t="shared" ref="D28" si="35">D26-D27</f>
         <v>31801</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" ref="E28:F28" si="31">E26-E27</f>
+        <f t="shared" ref="E28:F28" si="36">E26-E27</f>
         <v>38542</v>
       </c>
       <c r="F28" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>59302</v>
       </c>
       <c r="G28" s="4">
-        <f t="shared" ref="G28:J28" si="32">G26-G27</f>
+        <f t="shared" ref="G28:J28" si="37">G26-G27</f>
         <v>47767</v>
       </c>
       <c r="H28" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="37"/>
         <v>42587</v>
       </c>
       <c r="I28" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="37"/>
         <v>39510</v>
       </c>
       <c r="J28" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="37"/>
         <v>94958</v>
       </c>
       <c r="K28" s="4">
@@ -2590,11 +2996,11 @@
         <v>19230</v>
       </c>
       <c r="M28" s="4">
-        <f t="shared" ref="M28:N28" si="33">M26-M27</f>
+        <f t="shared" ref="M28:N28" si="38">M26-M27</f>
         <v>46942.479780000009</v>
       </c>
       <c r="N28" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>49134.397220000006</v>
       </c>
       <c r="O28" s="4"/>
@@ -2610,20 +3016,24 @@
       <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
       <c r="AA28" s="4"/>
-      <c r="AC28" s="3">
-        <f>AC26-AC27</f>
+      <c r="AB28" s="4"/>
+      <c r="AC28" s="4"/>
+      <c r="AD28" s="4"/>
+      <c r="AE28" s="4"/>
+      <c r="AG28" s="3">
+        <f>AG26-AG27</f>
         <v>159847</v>
       </c>
-      <c r="AD28" s="3">
-        <f>AD26-AD27</f>
+      <c r="AH28" s="3">
+        <f>AH26-AH27</f>
         <v>224822</v>
       </c>
-      <c r="AE28" s="3">
-        <f>AE26-AE27</f>
+      <c r="AI28" s="3">
+        <f>AI26-AI27</f>
         <v>138719.87699999998</v>
       </c>
     </row>
-    <row r="29" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>32</v>
       </c>
@@ -2671,14 +3081,18 @@
       <c r="X29" s="4"/>
       <c r="Y29" s="4"/>
       <c r="Z29" s="4"/>
-      <c r="AC29" s="3">
+      <c r="AA29" s="4"/>
+      <c r="AB29" s="4"/>
+      <c r="AC29" s="4"/>
+      <c r="AD29" s="4"/>
+      <c r="AG29" s="3">
         <v>122742</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AH29" s="3">
         <v>123788</v>
       </c>
     </row>
-    <row r="31" spans="2:36" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:40" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B31" s="5" t="s">
         <v>33</v>
       </c>
@@ -2687,19 +3101,19 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="9">
-        <f t="shared" ref="G31" si="34">G18/C18-1</f>
+        <f t="shared" ref="G31" si="39">G18/C18-1</f>
         <v>0.2520520057372877</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:J31" si="35">H18/D18-1</f>
+        <f t="shared" ref="H31:J31" si="40">H18/D18-1</f>
         <v>0.20347658052105189</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>0.13488564891946409</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>7.8694386881027034E-2</v>
       </c>
       <c r="K31" s="9">
@@ -2730,45 +3144,49 @@
       <c r="X31" s="9"/>
       <c r="Y31" s="9"/>
       <c r="Z31" s="9"/>
-      <c r="AD31" s="11">
-        <f>AD18/AC18-1</f>
+      <c r="AA31" s="9"/>
+      <c r="AB31" s="9"/>
+      <c r="AC31" s="9"/>
+      <c r="AD31" s="9"/>
+      <c r="AH31" s="11">
+        <f>AH18/AG18-1</f>
         <v>0.16191626008164883</v>
       </c>
-      <c r="AE31" s="11">
-        <f>AE18/AD18-1</f>
+      <c r="AI31" s="11">
+        <f>AI18/AH18-1</f>
         <v>-3.8161601662506373E-3</v>
       </c>
     </row>
-    <row r="32" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>83</v>
       </c>
       <c r="E32" s="13">
-        <f t="shared" ref="E32:K32" si="36">+E20/E18</f>
+        <f t="shared" ref="E32:K32" si="41">+E20/E18</f>
         <v>0.45156121708769442</v>
       </c>
       <c r="F32" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>0.44049854491318108</v>
       </c>
       <c r="G32" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>0.46292395586202817</v>
       </c>
       <c r="H32" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>0.45382217432499872</v>
       </c>
       <c r="I32" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>0.44073808721060914</v>
       </c>
       <c r="J32" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>0.4009834382889006</v>
       </c>
       <c r="K32" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>0.42130049973795131</v>
       </c>
       <c r="L32" s="13">
@@ -2776,28 +3194,71 @@
         <v>0.43173373920050134</v>
       </c>
       <c r="M32" s="13">
-        <f t="shared" ref="M32:N32" si="37">+M20/M18</f>
+        <f t="shared" ref="M32:AA32" si="42">+M20/M18</f>
         <v>0.44</v>
       </c>
       <c r="N32" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>0.44</v>
       </c>
-      <c r="O32" s="13"/>
-      <c r="P32" s="13"/>
-      <c r="Q32" s="13"/>
-      <c r="R32" s="13"/>
-      <c r="S32" s="13"/>
-      <c r="T32" s="13"/>
-      <c r="U32" s="13"/>
-      <c r="V32" s="13"/>
-      <c r="W32" s="13"/>
-      <c r="X32" s="13"/>
-      <c r="Y32" s="13"/>
-      <c r="Z32" s="13"/>
-      <c r="AD32" s="14"/>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="O32" s="13" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P32" s="13" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q32" s="13" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R32" s="13" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S32" s="13">
+        <f t="shared" si="42"/>
+        <v>0.5258274242794716</v>
+      </c>
+      <c r="T32" s="13">
+        <f t="shared" si="42"/>
+        <v>0.53312189278598787</v>
+      </c>
+      <c r="U32" s="13">
+        <f t="shared" si="42"/>
+        <v>0.53129018559389452</v>
+      </c>
+      <c r="V32" s="13">
+        <f t="shared" si="42"/>
+        <v>0.5256892012572052</v>
+      </c>
+      <c r="W32" s="13">
+        <f t="shared" si="42"/>
+        <v>0.55822621679572493</v>
+      </c>
+      <c r="X32" s="13">
+        <f t="shared" si="42"/>
+        <v>0.56916381216667389</v>
+      </c>
+      <c r="Y32" s="13">
+        <f t="shared" si="42"/>
+        <v>0.56410309588373453</v>
+      </c>
+      <c r="Z32" s="13">
+        <f t="shared" si="42"/>
+        <v>0.55712529132432309</v>
+      </c>
+      <c r="AA32" s="13">
+        <f t="shared" si="42"/>
+        <v>0.56635514970120837</v>
+      </c>
+      <c r="AB32" s="13"/>
+      <c r="AC32" s="13"/>
+      <c r="AD32" s="13"/>
+      <c r="AH32" s="14"/>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>84</v>
       </c>
@@ -2806,39 +3267,39 @@
         <v>0.13656525830010305</v>
       </c>
       <c r="F33" s="13">
-        <f t="shared" ref="F33:N33" si="38">+F27/F26</f>
+        <f t="shared" ref="F33:N33" si="43">+F27/F26</f>
         <v>5.986239259329719E-2</v>
       </c>
       <c r="G33" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.15086927151846979</v>
       </c>
       <c r="H33" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>8.7838416723783411E-2</v>
       </c>
       <c r="I33" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.13216333164935093</v>
       </c>
       <c r="J33" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>4.6539415420762502E-2</v>
       </c>
       <c r="K33" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.19271084752775672</v>
       </c>
       <c r="L33" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.19194890326918229</v>
       </c>
       <c r="M33" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.15</v>
       </c>
       <c r="N33" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.15</v>
       </c>
       <c r="O33" s="13"/>
@@ -2853,9 +3314,13 @@
       <c r="X33" s="13"/>
       <c r="Y33" s="13"/>
       <c r="Z33" s="13"/>
-      <c r="AD33" s="14"/>
-    </row>
-    <row r="34" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA33" s="13"/>
+      <c r="AB33" s="13"/>
+      <c r="AC33" s="13"/>
+      <c r="AD33" s="13"/>
+      <c r="AH33" s="14"/>
+    </row>
+    <row r="34" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -2880,8 +3345,12 @@
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
-    </row>
-    <row r="35" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA34" s="4"/>
+      <c r="AB34" s="4"/>
+      <c r="AC34" s="4"/>
+      <c r="AD34" s="4"/>
+    </row>
+    <row r="35" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
         <v>34</v>
       </c>
@@ -2915,8 +3384,12 @@
       <c r="X35" s="4"/>
       <c r="Y35" s="4"/>
       <c r="Z35" s="4"/>
-    </row>
-    <row r="36" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA35" s="4"/>
+      <c r="AB35" s="4"/>
+      <c r="AC35" s="4"/>
+      <c r="AD35" s="4"/>
+    </row>
+    <row r="36" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
         <v>35</v>
       </c>
@@ -2948,8 +3421,12 @@
       <c r="X36" s="4"/>
       <c r="Y36" s="4"/>
       <c r="Z36" s="4"/>
-    </row>
-    <row r="37" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA36" s="4"/>
+      <c r="AB36" s="4"/>
+      <c r="AC36" s="4"/>
+      <c r="AD36" s="4"/>
+    </row>
+    <row r="37" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
         <v>36</v>
       </c>
@@ -2981,8 +3458,12 @@
       <c r="X37" s="4"/>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
-    </row>
-    <row r="38" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA37" s="4"/>
+      <c r="AB37" s="4"/>
+      <c r="AC37" s="4"/>
+      <c r="AD37" s="4"/>
+    </row>
+    <row r="38" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
         <v>37</v>
       </c>
@@ -3014,8 +3495,12 @@
       <c r="X38" s="4"/>
       <c r="Y38" s="4"/>
       <c r="Z38" s="4"/>
-    </row>
-    <row r="39" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA38" s="4"/>
+      <c r="AB38" s="4"/>
+      <c r="AC38" s="4"/>
+      <c r="AD38" s="4"/>
+    </row>
+    <row r="39" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
         <v>38</v>
       </c>
@@ -3048,8 +3533,12 @@
       <c r="X39" s="4"/>
       <c r="Y39" s="4"/>
       <c r="Z39" s="4"/>
-    </row>
-    <row r="40" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA39" s="4"/>
+      <c r="AB39" s="4"/>
+      <c r="AC39" s="4"/>
+      <c r="AD39" s="4"/>
+    </row>
+    <row r="40" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
         <v>40</v>
       </c>
@@ -3081,8 +3570,12 @@
       <c r="X40" s="4"/>
       <c r="Y40" s="4"/>
       <c r="Z40" s="4"/>
-    </row>
-    <row r="41" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="4"/>
+      <c r="AC40" s="4"/>
+      <c r="AD40" s="4"/>
+    </row>
+    <row r="41" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
         <v>41</v>
       </c>
@@ -3116,8 +3609,12 @@
       <c r="X41" s="4"/>
       <c r="Y41" s="4"/>
       <c r="Z41" s="4"/>
-    </row>
-    <row r="42" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="4"/>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+    </row>
+    <row r="42" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
         <v>42</v>
       </c>
@@ -3151,8 +3648,12 @@
       <c r="X42" s="4"/>
       <c r="Y42" s="4"/>
       <c r="Z42" s="4"/>
-    </row>
-    <row r="43" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="4"/>
+      <c r="AC42" s="4"/>
+      <c r="AD42" s="4"/>
+    </row>
+    <row r="43" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
         <v>39</v>
       </c>
@@ -3186,8 +3687,12 @@
       <c r="X43" s="4"/>
       <c r="Y43" s="4"/>
       <c r="Z43" s="4"/>
-    </row>
-    <row r="44" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="4"/>
+      <c r="AC43" s="4"/>
+      <c r="AD43" s="4"/>
+    </row>
+    <row r="44" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -3212,8 +3717,12 @@
       <c r="X44" s="4"/>
       <c r="Y44" s="4"/>
       <c r="Z44" s="4"/>
-    </row>
-    <row r="45" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="4"/>
+      <c r="AC44" s="4"/>
+      <c r="AD44" s="4"/>
+    </row>
+    <row r="45" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
         <v>43</v>
       </c>
@@ -3247,8 +3756,12 @@
       <c r="X45" s="4"/>
       <c r="Y45" s="4"/>
       <c r="Z45" s="4"/>
-    </row>
-    <row r="46" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="4"/>
+      <c r="AC45" s="4"/>
+      <c r="AD45" s="4"/>
+    </row>
+    <row r="46" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
         <v>44</v>
       </c>
@@ -3282,8 +3795,12 @@
       <c r="X46" s="4"/>
       <c r="Y46" s="4"/>
       <c r="Z46" s="4"/>
-    </row>
-    <row r="47" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA46" s="4"/>
+      <c r="AB46" s="4"/>
+      <c r="AC46" s="4"/>
+      <c r="AD46" s="4"/>
+    </row>
+    <row r="47" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
         <v>29</v>
       </c>
@@ -3317,8 +3834,12 @@
       <c r="X47" s="4"/>
       <c r="Y47" s="4"/>
       <c r="Z47" s="4"/>
-    </row>
-    <row r="48" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA47" s="4"/>
+      <c r="AB47" s="4"/>
+      <c r="AC47" s="4"/>
+      <c r="AD47" s="4"/>
+    </row>
+    <row r="48" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
         <v>46</v>
       </c>
@@ -3352,8 +3873,12 @@
       <c r="X48" s="4"/>
       <c r="Y48" s="4"/>
       <c r="Z48" s="4"/>
-    </row>
-    <row r="49" spans="2:26" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA48" s="4"/>
+      <c r="AB48" s="4"/>
+      <c r="AC48" s="4"/>
+      <c r="AD48" s="4"/>
+    </row>
+    <row r="49" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
         <v>47</v>
       </c>
@@ -3387,8 +3912,12 @@
       <c r="X49" s="4"/>
       <c r="Y49" s="4"/>
       <c r="Z49" s="4"/>
-    </row>
-    <row r="50" spans="2:26" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA49" s="4"/>
+      <c r="AB49" s="4"/>
+      <c r="AC49" s="4"/>
+      <c r="AD49" s="4"/>
+    </row>
+    <row r="50" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
         <v>48</v>
       </c>
@@ -3420,8 +3949,12 @@
       <c r="X50" s="4"/>
       <c r="Y50" s="4"/>
       <c r="Z50" s="4"/>
-    </row>
-    <row r="51" spans="2:26" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA50" s="4"/>
+      <c r="AB50" s="4"/>
+      <c r="AC50" s="4"/>
+      <c r="AD50" s="4"/>
+    </row>
+    <row r="51" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
         <v>49</v>
       </c>
@@ -3455,8 +3988,12 @@
       <c r="X51" s="4"/>
       <c r="Y51" s="4"/>
       <c r="Z51" s="4"/>
-    </row>
-    <row r="53" spans="2:26" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA51" s="4"/>
+      <c r="AB51" s="4"/>
+      <c r="AC51" s="4"/>
+      <c r="AD51" s="4"/>
+    </row>
+    <row r="53" spans="2:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
         <v>82</v>
       </c>
@@ -3488,6 +4025,10 @@
       <c r="X53" s="4"/>
       <c r="Y53" s="4"/>
       <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
+      <c r="AB53" s="4"/>
+      <c r="AC53" s="4"/>
+      <c r="AD53" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
